--- a/data/EVALUACIONES/CAMPO/CAMPO.xlsx
+++ b/data/EVALUACIONES/CAMPO/CAMPO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30405"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30411"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\CAMPO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A9B959-6D1D-41AA-9DBA-613268366CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDD9E75-E1B7-4219-8CA3-1E8CA236D576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Fecha</t>
   </si>
@@ -114,22 +114,10 @@
     <t xml:space="preserve">Samuel_Chaparro_Garcia </t>
   </si>
   <si>
-    <t>5.67</t>
-  </si>
-  <si>
     <t>Alex_Palacios</t>
   </si>
   <si>
-    <t>-5.56</t>
-  </si>
-  <si>
     <t xml:space="preserve">Marco_Sanchez_Arias </t>
-  </si>
-  <si>
-    <t>-5.79</t>
-  </si>
-  <si>
-    <t>31.5</t>
   </si>
   <si>
     <t xml:space="preserve">Petko_Avramov </t>
@@ -257,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -269,13 +257,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -284,6 +266,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
+    <dxf>
+      <font>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -325,17 +318,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="10"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -412,10 +394,10 @@
     <tableColumn id="1" xr3:uid="{B90CC2EA-DED7-4B50-9C01-6648707B7686}" name="Fecha" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{49BFBD1B-88C4-49EF-ACC0-907CF6D29923}" name="Nombre" dataDxfId="5"/>
     <tableColumn id="11" xr3:uid="{2485B2B6-1AA4-4901-8B45-87383DB57039}" name="V_MAX" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{10A89B76-6E25-4687-86FC-402E5875F343}" name="AC_MAX" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{B6A95FF8-2A19-4995-B36D-CAC2D284919B}" name="DEC_MAX" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{6F0B8C04-FF29-4644-9965-73441115C769}" name="Tecnica_Sprint" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{ED7A1510-B4D4-448C-A7B6-385AEFB0314D}" name="Tecnica_COD" dataDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{10A89B76-6E25-4687-86FC-402E5875F343}" name="AC_MAX" dataDxfId="0"/>
+    <tableColumn id="13" xr3:uid="{B6A95FF8-2A19-4995-B36D-CAC2D284919B}" name="DEC_MAX" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{6F0B8C04-FF29-4644-9965-73441115C769}" name="Tecnica_Sprint" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{ED7A1510-B4D4-448C-A7B6-385AEFB0314D}" name="Tecnica_COD" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -759,14 +741,17 @@
       <c r="B2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="9">
-        <v>32944</v>
-      </c>
-      <c r="D2" s="9">
-        <v>5934</v>
-      </c>
-      <c r="E2" s="9">
-        <v>-5147</v>
+      <c r="C2">
+        <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
+        <v>32.944000000000003</v>
+      </c>
+      <c r="D2">
+        <f ca="1">Tabla1[[#This Row],[AC_MAX]]/1000</f>
+        <v>5.9340000000000002</v>
+      </c>
+      <c r="E2">
+        <f ca="1">Tabla1[[#This Row],[DEC_MAX]]/1000</f>
+        <v>-5.1470000000000002</v>
       </c>
       <c r="F2" s="4">
         <v>2</v>
@@ -782,14 +767,17 @@
       <c r="B3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="9">
-        <v>32864</v>
-      </c>
-      <c r="D3" s="9">
-        <v>5486</v>
-      </c>
-      <c r="E3" s="9">
-        <v>-5222</v>
+      <c r="C3">
+        <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
+        <v>32.863999999999997</v>
+      </c>
+      <c r="D3">
+        <f ca="1">Tabla1[[#This Row],[AC_MAX]]/1000</f>
+        <v>5.4859999999999998</v>
+      </c>
+      <c r="E3">
+        <f ca="1">Tabla1[[#This Row],[DEC_MAX]]/1000</f>
+        <v>-5.2220000000000004</v>
       </c>
       <c r="F3" s="6">
         <v>1.5</v>
@@ -805,14 +793,17 @@
       <c r="B4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="9">
-        <v>34607</v>
-      </c>
-      <c r="D4" s="9">
-        <v>5482</v>
-      </c>
-      <c r="E4" s="9">
-        <v>-5134</v>
+      <c r="C4">
+        <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
+        <v>34.606999999999999</v>
+      </c>
+      <c r="D4">
+        <f ca="1">Tabla1[[#This Row],[AC_MAX]]/1000</f>
+        <v>5.4820000000000002</v>
+      </c>
+      <c r="E4">
+        <f ca="1">Tabla1[[#This Row],[DEC_MAX]]/1000</f>
+        <v>-5.1340000000000003</v>
       </c>
       <c r="F4">
         <v>1.5</v>
@@ -825,17 +816,20 @@
       <c r="A5" s="1">
         <v>46247</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="9">
-        <v>30888</v>
-      </c>
-      <c r="D5" s="9">
-        <v>5368</v>
-      </c>
-      <c r="E5" s="9">
-        <v>-5017</v>
+      <c r="C5">
+        <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
+        <v>30.888000000000002</v>
+      </c>
+      <c r="D5">
+        <f ca="1">Tabla1[[#This Row],[AC_MAX]]/1000</f>
+        <v>5.3680000000000003</v>
+      </c>
+      <c r="E5">
+        <f ca="1">Tabla1[[#This Row],[DEC_MAX]]/1000</f>
+        <v>-5.0170000000000003</v>
       </c>
       <c r="F5" s="4">
         <v>2</v>
@@ -851,9 +845,18 @@
       <c r="B6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+      <c r="C6">
+        <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f ca="1">Tabla1[[#This Row],[AC_MAX]]/1000</f>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f ca="1">Tabla1[[#This Row],[DEC_MAX]]/1000</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
@@ -862,14 +865,17 @@
       <c r="B7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="9">
-        <v>33037</v>
-      </c>
-      <c r="D7" s="9">
-        <v>5782</v>
-      </c>
-      <c r="E7" s="9">
-        <v>-4989</v>
+      <c r="C7">
+        <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
+        <v>33.036999999999999</v>
+      </c>
+      <c r="D7">
+        <f ca="1">Tabla1[[#This Row],[AC_MAX]]/1000</f>
+        <v>5.782</v>
+      </c>
+      <c r="E7">
+        <f ca="1">Tabla1[[#This Row],[DEC_MAX]]/1000</f>
+        <v>-4.9889999999999999</v>
       </c>
       <c r="F7" s="6">
         <v>1.5</v>
@@ -882,17 +888,20 @@
       <c r="A8" s="1">
         <v>46247</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="9">
-        <v>32753</v>
-      </c>
-      <c r="D8" s="9">
-        <v>5916</v>
-      </c>
-      <c r="E8" s="9">
-        <v>-5417</v>
+      <c r="C8">
+        <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
+        <v>32.753</v>
+      </c>
+      <c r="D8">
+        <f ca="1">Tabla1[[#This Row],[AC_MAX]]/1000</f>
+        <v>5.9160000000000004</v>
+      </c>
+      <c r="E8">
+        <f ca="1">Tabla1[[#This Row],[DEC_MAX]]/1000</f>
+        <v>-5.4169999999999998</v>
       </c>
       <c r="F8" s="4">
         <v>2</v>
@@ -908,14 +917,17 @@
       <c r="B9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="9">
-        <v>31554</v>
-      </c>
-      <c r="D9" s="9">
-        <v>6362</v>
-      </c>
-      <c r="E9" s="9">
-        <v>-5476</v>
+      <c r="C9">
+        <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
+        <v>31.553999999999998</v>
+      </c>
+      <c r="D9">
+        <f ca="1">Tabla1[[#This Row],[AC_MAX]]/1000</f>
+        <v>6.3620000000000001</v>
+      </c>
+      <c r="E9">
+        <f ca="1">Tabla1[[#This Row],[DEC_MAX]]/1000</f>
+        <v>-5.476</v>
       </c>
       <c r="F9" s="4">
         <v>2</v>
@@ -931,14 +943,17 @@
       <c r="B10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="9">
-        <v>32335</v>
-      </c>
-      <c r="D10" s="9">
-        <v>5536</v>
-      </c>
-      <c r="E10" s="9">
-        <v>-5405</v>
+      <c r="C10">
+        <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
+        <v>32.335000000000001</v>
+      </c>
+      <c r="D10">
+        <f ca="1">Tabla1[[#This Row],[AC_MAX]]/1000</f>
+        <v>5.5359999999999996</v>
+      </c>
+      <c r="E10">
+        <f ca="1">Tabla1[[#This Row],[DEC_MAX]]/1000</f>
+        <v>-5.4050000000000002</v>
       </c>
       <c r="F10" s="4">
         <v>2</v>
@@ -954,14 +969,17 @@
       <c r="B11" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="9">
-        <v>31946</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-5714</v>
+      <c r="C11">
+        <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
+        <v>31.946000000000002</v>
+      </c>
+      <c r="D11">
+        <f ca="1">Tabla1[[#This Row],[AC_MAX]]/1000</f>
+        <v>5.67</v>
+      </c>
+      <c r="E11">
+        <f ca="1">Tabla1[[#This Row],[DEC_MAX]]/1000</f>
+        <v>-5.7140000000000004</v>
       </c>
       <c r="F11" s="6">
         <v>2</v>
@@ -975,21 +993,24 @@
         <v>46247</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="9">
-        <v>33793</v>
-      </c>
-      <c r="D12" s="9">
-        <v>5523</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="12">
+        <v>29</v>
+      </c>
+      <c r="C12">
+        <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
+        <v>33.792999999999999</v>
+      </c>
+      <c r="D12">
+        <f ca="1">Tabla1[[#This Row],[AC_MAX]]/1000</f>
+        <v>5.5229999999999997</v>
+      </c>
+      <c r="E12">
+        <f ca="1">Tabla1[[#This Row],[DEC_MAX]]/1000</f>
+        <v>-5.56</v>
+      </c>
+      <c r="F12" s="10">
         <v>2.5</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="11">
         <v>2.5</v>
       </c>
     </row>
@@ -997,17 +1018,20 @@
       <c r="A13" s="1">
         <v>46247</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="9">
-        <v>31446</v>
-      </c>
-      <c r="D13" s="9">
-        <v>6254</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>33</v>
+      <c r="B13" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13">
+        <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
+        <v>31.446000000000002</v>
+      </c>
+      <c r="D13">
+        <f ca="1">Tabla1[[#This Row],[AC_MAX]]/1000</f>
+        <v>6.2539999999999996</v>
+      </c>
+      <c r="E13">
+        <f ca="1">Tabla1[[#This Row],[DEC_MAX]]/1000</f>
+        <v>-5.79</v>
       </c>
       <c r="F13" s="6">
         <v>1.5</v>
@@ -1023,14 +1047,17 @@
       <c r="B14" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="9">
-        <v>29848</v>
-      </c>
-      <c r="D14" s="9">
-        <v>5569</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-5475</v>
+      <c r="C14">
+        <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
+        <v>29.847999999999999</v>
+      </c>
+      <c r="D14">
+        <f ca="1">Tabla1[[#This Row],[AC_MAX]]/1000</f>
+        <v>5.569</v>
+      </c>
+      <c r="E14">
+        <f ca="1">Tabla1[[#This Row],[DEC_MAX]]/1000</f>
+        <v>-5.4749999999999996</v>
       </c>
       <c r="F14" s="6">
         <v>1.5</v>
@@ -1046,14 +1073,17 @@
       <c r="B15" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="9">
-        <v>5739</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-5166</v>
+      <c r="C15">
+        <f ca="1">Tabla1[[#This Row],[V_MAX]]/1000</f>
+        <v>31.5</v>
+      </c>
+      <c r="D15">
+        <f ca="1">Tabla1[[#This Row],[AC_MAX]]/1000</f>
+        <v>5.7389999999999999</v>
+      </c>
+      <c r="E15">
+        <f ca="1">Tabla1[[#This Row],[DEC_MAX]]/1000</f>
+        <v>-5.1660000000000004</v>
       </c>
       <c r="F15" s="6">
         <v>2</v>
@@ -1066,16 +1096,16 @@
       <c r="A16" s="1">
         <v>46247</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="10">
+      <c r="B16" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="9">
         <v>34.037999999999997</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <v>5.9050000000000002</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <v>-5.359</v>
       </c>
       <c r="F16" s="6">
@@ -1092,19 +1122,19 @@
       <c r="B17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <v>31.013999999999999</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>6.5890000000000004</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <v>-5.2969999999999997</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <v>0.5</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1112,16 +1142,16 @@
       <c r="A18" s="1">
         <v>46247</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="10">
+      <c r="B18" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="9">
         <v>33.188000000000002</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <v>6.3090000000000002</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <v>-5.6630000000000003</v>
       </c>
       <c r="F18" s="6">
@@ -1138,13 +1168,13 @@
       <c r="B19" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <v>31.391999999999999</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>5.3540000000000001</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <v>-5.0030000000000001</v>
       </c>
       <c r="F19" s="6">
@@ -1161,13 +1191,13 @@
       <c r="B20" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <v>34.451999999999998</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>5.7370000000000001</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="9">
         <v>-5.157</v>
       </c>
       <c r="F20" s="4">
@@ -1184,13 +1214,13 @@
       <c r="B21" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <v>33.707000000000001</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>5.4630000000000001</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="9">
         <v>-5.319</v>
       </c>
       <c r="F21" s="6">
@@ -1204,16 +1234,16 @@
       <c r="A22" s="1">
         <v>46247</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="10">
+      <c r="B22" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="9">
         <v>31.914000000000001</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <v>5.4569999999999999</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="9">
         <v>-6.2229999999999999</v>
       </c>
       <c r="F22" s="4">
@@ -1230,13 +1260,13 @@
       <c r="B23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="9">
         <v>34.530999999999999</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="9">
         <v>5.4649999999999999</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="9">
         <v>-6.8460000000000001</v>
       </c>
       <c r="F23" s="6">
@@ -1253,13 +1283,13 @@
       <c r="B24" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="9">
         <v>32.926000000000002</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="9">
         <v>5.423</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="9">
         <v>-5.3360000000000003</v>
       </c>
       <c r="F24" s="4">
@@ -1273,16 +1303,16 @@
       <c r="A25" s="1">
         <v>46247</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="9">
         <v>30.888000000000002</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="9">
         <v>5.12</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="9">
         <v>-5.0259999999999998</v>
       </c>
       <c r="F25" s="6">
@@ -1296,16 +1326,16 @@
       <c r="A26" s="1">
         <v>46247</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C26" s="10">
+      <c r="B26" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="9">
         <v>31.414000000000001</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="9">
         <v>5.7859999999999996</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="9">
         <v>-5.2619999999999996</v>
       </c>
       <c r="F26" s="4">
@@ -1322,13 +1352,13 @@
       <c r="B27" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="9">
         <v>32.256</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="9">
         <v>5.3710000000000004</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="9">
         <v>-4.9400000000000004</v>
       </c>
       <c r="F27" s="4">
@@ -1345,13 +1375,13 @@
       <c r="B28" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="9">
         <v>29.74</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="9">
         <v>5.4260000000000002</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="9">
         <v>-5.1349999999999998</v>
       </c>
       <c r="F28" s="4">
@@ -1368,13 +1398,13 @@
       <c r="B29" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="9">
         <v>33.616999999999997</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="9">
         <v>5.5529999999999999</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="9">
         <v>-4.8680000000000003</v>
       </c>
       <c r="F29" s="4">
